--- a/file_X_Tuesday_6_7_student_data.xlsx
+++ b/file_X_Tuesday_6_7_student_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\29abh\Projects\RAC_Projects\RACOperationalApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734C9BAB-B6BB-4E59-A62B-D82870F5F74B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35D794F-04E1-422B-AA2F-72BBF9628D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="690" windowWidth="38380" windowHeight="20140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Result" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>Name</t>
   </si>
@@ -37,27 +37,6 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>Rannver</t>
-  </si>
-  <si>
-    <t>4, 5, 9 (diagram), 18, 20 (diagram)</t>
-  </si>
-  <si>
-    <t>Abhishek</t>
-  </si>
-  <si>
-    <t>adlk;lk;la;sd;l;a</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
     <t xml:space="preserve">Name </t>
   </si>
   <si>
@@ -65,19 +44,202 @@
   </si>
   <si>
     <t>Roll Number</t>
+  </si>
+  <si>
+    <t>Aahan Mehta</t>
+  </si>
+  <si>
+    <t>Aalap Kansal</t>
+  </si>
+  <si>
+    <t>Aaradhya Pundir</t>
+  </si>
+  <si>
+    <t>Aarav Tewatia</t>
+  </si>
+  <si>
+    <t>Aarav Vashisth</t>
+  </si>
+  <si>
+    <t>Aarav Yaadav</t>
+  </si>
+  <si>
+    <t>Advay Arora</t>
+  </si>
+  <si>
+    <t>Agamjyot Singh</t>
+  </si>
+  <si>
+    <t>Ahan Chaudhary</t>
+  </si>
+  <si>
+    <t>Ansh Paliwal</t>
+  </si>
+  <si>
+    <t>Aradhya Kaushik</t>
+  </si>
+  <si>
+    <t>Arnav Mittal</t>
+  </si>
+  <si>
+    <t>Avanika Biju</t>
+  </si>
+  <si>
+    <t>Ayushman Sharma</t>
+  </si>
+  <si>
+    <t>Bhavish</t>
+  </si>
+  <si>
+    <t>Deeshee</t>
+  </si>
+  <si>
+    <t>Devansh Kaushik</t>
+  </si>
+  <si>
+    <t>Dhruv Bahradwaj</t>
+  </si>
+  <si>
+    <t>Dhruv Khattar</t>
+  </si>
+  <si>
+    <t>Divyanshi Singh</t>
+  </si>
+  <si>
+    <t>Gauransh Kalra</t>
+  </si>
+  <si>
+    <t>Gauranshi Garg</t>
+  </si>
+  <si>
+    <t>Genia Gupta</t>
+  </si>
+  <si>
+    <t>Harshaman</t>
+  </si>
+  <si>
+    <t>Shaurya</t>
+  </si>
+  <si>
+    <t>Itish Chopra</t>
+  </si>
+  <si>
+    <t>Janvi</t>
+  </si>
+  <si>
+    <t>Japish</t>
+  </si>
+  <si>
+    <t>Jasleen</t>
+  </si>
+  <si>
+    <t>Kanishka Baid</t>
+  </si>
+  <si>
+    <t>Kartik</t>
+  </si>
+  <si>
+    <t>Kavyansh Malra</t>
+  </si>
+  <si>
+    <t>Khushi Chaudhary</t>
+  </si>
+  <si>
+    <t>Khyati gupta</t>
+  </si>
+  <si>
+    <t>Krisha</t>
+  </si>
+  <si>
+    <t>Krishjyot</t>
+  </si>
+  <si>
+    <t>Laavanya Gupta</t>
+  </si>
+  <si>
+    <t>Mahi Tripathi</t>
+  </si>
+  <si>
+    <t>Dhairya</t>
+  </si>
+  <si>
+    <t>Nitya</t>
+  </si>
+  <si>
+    <t>Pranshi Bedi</t>
+  </si>
+  <si>
+    <t>Pratham Gupta</t>
+  </si>
+  <si>
+    <t>Shristi Naidu</t>
+  </si>
+  <si>
+    <t>Riyansh Singh</t>
+  </si>
+  <si>
+    <t>Saisha Dhir</t>
+  </si>
+  <si>
+    <t>Samaira</t>
+  </si>
+  <si>
+    <t>Seerat</t>
+  </si>
+  <si>
+    <t>Pavani</t>
+  </si>
+  <si>
+    <t>Siddhi Chandna</t>
+  </si>
+  <si>
+    <t>Siddhi Garg</t>
+  </si>
+  <si>
+    <t>Siddhika</t>
+  </si>
+  <si>
+    <t>Riddhika</t>
+  </si>
+  <si>
+    <t>Srishti Goel</t>
+  </si>
+  <si>
+    <t>Viddhi</t>
+  </si>
+  <si>
+    <t>Vihaan Gupta</t>
+  </si>
+  <si>
+    <t>Vihaan Chataurvedi</t>
+  </si>
+  <si>
+    <t>Yashvi</t>
+  </si>
+  <si>
+    <t>Yuvraj Singh</t>
+  </si>
+  <si>
+    <t>Zoya</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -88,7 +250,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -96,13 +258,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -383,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.36328125" customWidth="1"/>
@@ -401,61 +584,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
-        <v>33</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>40</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>39</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
-        <v>39.5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -463,63 +591,495 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FC8ABDE-9CD1-46A8-811F-2734DD2C7292}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="31.453125" customWidth="1"/>
-    <col min="2" max="2" width="26.26953125" customWidth="1"/>
+    <col min="2" max="2" width="26.26953125" style="1" customWidth="1"/>
     <col min="3" max="3" width="28.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3">
+        <v>919971110980</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3">
+        <v>919910309295</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3">
+        <v>919717110497</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3">
+        <v>919990927054</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B6" s="3">
+        <v>919717021141</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B7" s="3">
+        <v>917838350790</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
-        <v>9811658385</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>9811658385</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>9811658385</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
-        <v>9811658385</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1">
-        <v>919811658385</v>
+      <c r="B8" s="3">
+        <v>919650035580</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="3">
+        <v>918860697593</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="3">
+        <v>918800192759</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="3">
+        <v>919871693443</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="3">
+        <v>917001058288</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="3">
+        <v>919468408950</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="3">
+        <v>919560317939</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="3">
+        <v>919212155286</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="3">
+        <v>917838293405</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="3">
+        <v>919654969631</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="3">
+        <v>919718064063</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="3">
+        <v>919999417099</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="3">
+        <v>918447035790</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="3">
+        <v>919990414782</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="3">
+        <v>919891826139</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="3">
+        <v>919811883731</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="3">
+        <v>919877102306</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="3">
+        <v>919810253006</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="3">
+        <v>919958968029</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="3">
+        <v>917838067389</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="3">
+        <v>919289505137</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="3">
+        <v>919211576081</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="3">
+        <v>919654906656</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="3">
+        <v>919810108081</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="3">
+        <v>919873277871</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="3">
+        <v>919958007793</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="3">
+        <v>917678469620</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="3">
+        <v>919015543111</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="3">
+        <v>919811882066</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="3">
+        <v>919818170725</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="3">
+        <v>919873934381</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="3">
+        <v>919911182706</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="3">
+        <v>919810576319</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="3">
+        <v>919289895017</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42" s="3">
+        <v>919818292054</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" s="3">
+        <v>918368183326</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" s="3">
+        <v>919891886765</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="3">
+        <v>919718017480</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" s="3">
+        <v>919711194841</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="3">
+        <v>919999579035</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" s="3">
+        <v>919999867574</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" s="3">
+        <v>919355161777</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" s="3">
+        <v>918802658408</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" s="3">
+        <v>919810778310</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" s="3">
+        <v>919811284252</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" s="3">
+        <v>919811284252</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" s="3">
+        <v>919015910011</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" s="3">
+        <v>919873917730</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56" s="3">
+        <v>918878001001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="3">
+        <v>918750230707</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" s="3">
+        <v>919289200560</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B59" s="3">
+        <v>918685066066</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" s="3">
+        <v>919711559477</v>
       </c>
     </row>
   </sheetData>

--- a/file_X_Tuesday_6_7_student_data.xlsx
+++ b/file_X_Tuesday_6_7_student_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\29abh\Projects\RAC_Projects\RACOperationalApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBF3D3E-043D-4C18-AEE9-C3C457072850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC8D5BF-ECE6-436E-8C34-2D8F3B5FA82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="28800" windowHeight="15370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22540" yWindow="10430" windowWidth="14240" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Result" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Name</t>
   </si>
@@ -44,6 +44,12 @@
   </si>
   <si>
     <t>Roll Number</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>9,2,5,6,6,66</t>
   </si>
 </sst>
 </file>
@@ -389,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.36328125" customWidth="1"/>
@@ -405,6 +411,17 @@
       </c>
       <c r="C1" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>39.5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
